--- a/data/trans_bre/P3A_R1-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R1-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,88; -0,26</t>
+          <t>-8,45; -1,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,09; -9,35</t>
+          <t>-17,82; -8,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,79; -9,65</t>
+          <t>-18,28; -9,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,61; -0,41</t>
+          <t>-10,11; -0,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,56; -1,84</t>
+          <t>-46,66; -7,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-64,23; -40,47</t>
+          <t>-63,78; -38,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,11; -38,22</t>
+          <t>-61,03; -37,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,68; -1,85</t>
+          <t>-36,76; -1,43</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,08; -6,12</t>
+          <t>-13,22; -6,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,66; -10,37</t>
+          <t>-17,56; -10,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,69; -7,73</t>
+          <t>-15,77; -8,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 11,84</t>
+          <t>-6,98; 11,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,59; -33,71</t>
+          <t>-59,71; -36,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,01; -39,93</t>
+          <t>-58,88; -39,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,7; -26,03</t>
+          <t>-47,5; -27,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 87,67</t>
+          <t>-22,99; 89,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,32; -5,68</t>
+          <t>-14,5; -5,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,96; -5,62</t>
+          <t>-14,37; -5,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,22; -7,44</t>
+          <t>-16,31; -7,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,75; -6,95</t>
+          <t>-24,75; -6,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,67; -26,02</t>
+          <t>-53,94; -25,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,47; -22,09</t>
+          <t>-50,56; -24,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,47; -24,91</t>
+          <t>-46,58; -23,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-69,28; -22,62</t>
+          <t>-71,94; -22,56</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,58; -6,45</t>
+          <t>-13,84; -7,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,41; -8,83</t>
+          <t>-16,58; -8,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,35; -13,31</t>
+          <t>-21,05; -13,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,48; -7,21</t>
+          <t>-16,08; -7,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,74; -30,49</t>
+          <t>-55,21; -32,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,39; -32,16</t>
+          <t>-52,06; -32,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,51; -38,66</t>
+          <t>-54,38; -38,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,82; -28,22</t>
+          <t>-52,57; -28,83</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -7,06</t>
+          <t>-10,78; -7,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -10,56</t>
+          <t>-14,62; -10,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -11,73</t>
+          <t>-16,0; -11,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -1,5</t>
+          <t>-10,67; -1,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,24; -35,97</t>
+          <t>-48,63; -35,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-51,08; -39,8</t>
+          <t>-50,98; -40,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,73; -37,36</t>
+          <t>-47,6; -37,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,19; -9,71</t>
+          <t>-37,77; -7,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R1-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R1-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,03</t>
+          <t>-4,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-19,63%</t>
+          <t>-15,83%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,45; -1,18</t>
+          <t>-8,02; -0,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,82; -8,76</t>
+          <t>-17,85; -9,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -9,71</t>
+          <t>-18,61; -9,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,11; -0,23</t>
+          <t>-8,59; 0,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,66; -7,79</t>
+          <t>-46,02; -3,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,78; -38,37</t>
+          <t>-63,53; -39,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-61,03; -37,61</t>
+          <t>-62,15; -38,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,76; -1,43</t>
+          <t>-30,04; 0,21</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>-6,45</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>-21,83%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,22; -6,55</t>
+          <t>-13,04; -5,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,56; -10,12</t>
+          <t>-17,76; -10,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -8,03</t>
+          <t>-16,07; -7,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 11,86</t>
+          <t>-10,24; -2,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,71; -36,63</t>
+          <t>-59,36; -32,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,88; -39,4</t>
+          <t>-59,06; -39,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,5; -27,29</t>
+          <t>-47,69; -27,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 89,25</t>
+          <t>-32,44; -9,66</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-14,11</t>
+          <t>-8,69</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-43,69%</t>
+          <t>-26,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,5; -5,65</t>
+          <t>-14,45; -6,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -5,79</t>
+          <t>-15,29; -6,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,31; -7,06</t>
+          <t>-16,63; -7,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,75; -6,83</t>
+          <t>-13,22; -4,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,94; -25,49</t>
+          <t>-54,1; -28,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,56; -24,06</t>
+          <t>-51,42; -25,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,58; -23,76</t>
+          <t>-46,95; -23,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,94; -22,56</t>
+          <t>-37,78; -15,12</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-11,33</t>
+          <t>-10,38</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-39,95%</t>
+          <t>-36,73%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -7,15</t>
+          <t>-13,87; -6,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,58; -8,75</t>
+          <t>-16,66; -9,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,05; -13,09</t>
+          <t>-21,03; -13,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,08; -7,39</t>
+          <t>-14,0; -6,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,21; -32,36</t>
+          <t>-54,99; -32,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,06; -32,12</t>
+          <t>-52,44; -32,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,38; -38,28</t>
+          <t>-54,4; -38,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,57; -28,83</t>
+          <t>-45,67; -26,7</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-7,14</t>
+          <t>-7,7</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-26,48%</t>
+          <t>-26,51%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -7,15</t>
+          <t>-10,64; -7,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -10,58</t>
+          <t>-14,51; -10,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,0; -11,9</t>
+          <t>-15,71; -11,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -1,12</t>
+          <t>-9,73; -5,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,63; -35,34</t>
+          <t>-48,97; -34,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-50,98; -40,18</t>
+          <t>-50,67; -39,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,6; -37,84</t>
+          <t>-47,31; -37,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-37,77; -7,67</t>
+          <t>-31,93; -20,2</t>
         </is>
       </c>
     </row>
